--- a/output/pdf_financials_xlsx/MILI.xlsx
+++ b/output/pdf_financials_xlsx/MILI.xlsx
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.794365</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.229681</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.473075</v>
       </c>
     </row>
     <row r="93">
@@ -3049,7 +3049,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3431,7 +3435,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.794365</v>
       </c>

--- a/output/pdf_financials_xlsx/MILI.xlsx
+++ b/output/pdf_financials_xlsx/MILI.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005718</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.064489</v>
       </c>
     </row>
     <row r="13">
@@ -870,10 +870,10 @@
         <v>-3.421304</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.707041</v>
+        <v>-0.712759</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.665004</v>
+        <v>-6.729493</v>
       </c>
     </row>
     <row r="28">
@@ -902,10 +902,10 @@
         <v>-3.421304</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.707041</v>
+        <v>-0.712759</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.665004</v>
+        <v>-6.729493</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008359</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.022192</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.607125</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008359</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.022192</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.607125</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.008359</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.022192</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.657499</v>
+        <v>0.050374</v>
       </c>
     </row>
     <row r="49">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">

--- a/output/pdf_financials_xlsx/MILI.xlsx
+++ b/output/pdf_financials_xlsx/MILI.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.276453</v>
+        <v>0.321453</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.04375</v>
+        <v>0.10375</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.386917</v>
+        <v>2.498917</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.656985</v>
+        <v>0.701985</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.248427</v>
+        <v>0.308427</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.751489</v>
+        <v>2.863489</v>
       </c>
     </row>
     <row r="11">
@@ -2238,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.039894</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.007228</v>
       </c>
     </row>
     <row r="111">
@@ -3629,7 +3629,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4138,7 +4142,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -5951,7 +5959,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -6763,7 +6775,11 @@
           <t>Directors’ fees (Note 12)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>0.045</v>
       </c>
